--- a/OCT_2026/Reports/Monthly.xlsx
+++ b/OCT_2026/Reports/Monthly.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Sep_2026\Daily Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED80155-2192-4F1A-891E-30F3663DAC53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC69D6E9-EA49-4EF9-8277-033BF1D51500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{3E645682-E893-4F6E-94AA-185947CE66D6}"/>
   </bookViews>
@@ -93,7 +93,7 @@
     <t>Primary</t>
   </si>
   <si>
-    <t>Sep</t>
+    <t>OCT</t>
   </si>
 </sst>
 </file>
@@ -133,7 +133,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -161,12 +161,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -218,7 +212,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -262,7 +256,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -592,33 +585,34 @@
     <col min="3" max="3" width="5.26953125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.7265625" customWidth="1"/>
     <col min="5" max="5" width="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="8.7265625" customWidth="1"/>
+    <col min="6" max="7" width="8.7265625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="8.7265625" customWidth="1"/>
     <col min="9" max="9" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="2.6328125" customWidth="1"/>
-    <col min="11" max="11" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.26953125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="2.453125" customWidth="1"/>
-    <col min="15" max="15" width="6.90625" customWidth="1"/>
-    <col min="16" max="16" width="9.453125" customWidth="1"/>
-    <col min="17" max="17" width="7.1796875" customWidth="1"/>
-    <col min="18" max="20" width="9.453125" customWidth="1"/>
-    <col min="21" max="21" width="2.90625" customWidth="1"/>
-    <col min="22" max="22" width="8.26953125" customWidth="1"/>
-    <col min="23" max="23" width="9.453125" customWidth="1"/>
-    <col min="24" max="24" width="7.81640625" customWidth="1"/>
-    <col min="25" max="27" width="9.453125" customWidth="1"/>
-    <col min="28" max="28" width="3.08984375" customWidth="1"/>
-    <col min="29" max="29" width="8.6328125" customWidth="1"/>
-    <col min="30" max="30" width="7" customWidth="1"/>
-    <col min="31" max="31" width="6.1796875" customWidth="1"/>
-    <col min="32" max="32" width="7.54296875" customWidth="1"/>
-    <col min="33" max="33" width="6.453125" customWidth="1"/>
-    <col min="34" max="34" width="7.453125" customWidth="1"/>
-    <col min="35" max="35" width="8.6328125" customWidth="1"/>
-    <col min="36" max="36" width="6.453125" customWidth="1"/>
-    <col min="37" max="37" width="8.6328125" customWidth="1"/>
-    <col min="38" max="38" width="7.54296875" customWidth="1"/>
+    <col min="10" max="10" width="6.6328125" customWidth="1"/>
+    <col min="11" max="11" width="5.81640625" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="6.26953125" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="7.36328125" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="2.453125" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="6.90625" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="9.453125" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="7.1796875" hidden="1" customWidth="1"/>
+    <col min="18" max="20" width="9.453125" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="2.90625" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="8.26953125" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="9.453125" hidden="1" customWidth="1"/>
+    <col min="24" max="24" width="7.81640625" hidden="1" customWidth="1"/>
+    <col min="25" max="27" width="9.453125" hidden="1" customWidth="1"/>
+    <col min="28" max="28" width="3.08984375" hidden="1" customWidth="1"/>
+    <col min="29" max="29" width="8.6328125" hidden="1" customWidth="1"/>
+    <col min="30" max="30" width="7" hidden="1" customWidth="1"/>
+    <col min="31" max="31" width="6.1796875" hidden="1" customWidth="1"/>
+    <col min="32" max="32" width="7.54296875" hidden="1" customWidth="1"/>
+    <col min="33" max="33" width="6.453125" hidden="1" customWidth="1"/>
+    <col min="34" max="34" width="7.453125" hidden="1" customWidth="1"/>
+    <col min="35" max="35" width="8.6328125" hidden="1" customWidth="1"/>
+    <col min="36" max="36" width="6.453125" hidden="1" customWidth="1"/>
+    <col min="37" max="37" width="8.6328125" hidden="1" customWidth="1"/>
+    <col min="38" max="38" width="7.54296875" hidden="1" customWidth="1"/>
     <col min="39" max="39" width="9.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -626,47 +620,47 @@
       <c r="A1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="19"/>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
-      <c r="R1" s="19"/>
-      <c r="S1" s="19"/>
-      <c r="T1" s="19"/>
-      <c r="U1" s="19"/>
-      <c r="V1" s="19"/>
-      <c r="W1" s="19"/>
-      <c r="X1" s="19"/>
-      <c r="Y1" s="19"/>
-      <c r="Z1" s="19"/>
-      <c r="AA1" s="19"/>
-      <c r="AB1" s="19"/>
-      <c r="AC1" s="19"/>
-      <c r="AD1" s="19"/>
-      <c r="AE1" s="19"/>
-      <c r="AF1" s="19"/>
-      <c r="AG1" s="19"/>
-      <c r="AH1" s="19"/>
-      <c r="AI1" s="19"/>
-      <c r="AJ1" s="19"/>
-      <c r="AK1" s="19"/>
-      <c r="AL1" s="19"/>
-      <c r="AM1" s="19"/>
-      <c r="AN1" s="19"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
+      <c r="Q1" s="18"/>
+      <c r="R1" s="18"/>
+      <c r="S1" s="18"/>
+      <c r="T1" s="18"/>
+      <c r="U1" s="18"/>
+      <c r="V1" s="18"/>
+      <c r="W1" s="18"/>
+      <c r="X1" s="18"/>
+      <c r="Y1" s="18"/>
+      <c r="Z1" s="18"/>
+      <c r="AA1" s="18"/>
+      <c r="AB1" s="18"/>
+      <c r="AC1" s="18"/>
+      <c r="AD1" s="18"/>
+      <c r="AE1" s="18"/>
+      <c r="AF1" s="18"/>
+      <c r="AG1" s="18"/>
+      <c r="AH1" s="18"/>
+      <c r="AI1" s="18"/>
+      <c r="AJ1" s="18"/>
+      <c r="AK1" s="18"/>
+      <c r="AL1" s="18"/>
+      <c r="AM1" s="18"/>
+      <c r="AN1" s="18"/>
     </row>
     <row r="2" spans="1:40" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="3" t="s">
@@ -679,13 +673,13 @@
         <v>0</v>
       </c>
       <c r="E2" s="14">
-        <v>46270</v>
+        <v>46296</v>
       </c>
       <c r="F2" s="14">
-        <v>46276</v>
+        <v>46296</v>
       </c>
       <c r="G2" s="14">
-        <v>46288</v>
+        <v>46296</v>
       </c>
       <c r="H2" s="14" t="s">
         <v>21</v>
@@ -795,79 +789,43 @@
         <v>70</v>
       </c>
       <c r="D3" s="1">
-        <v>7895</v>
+        <v>10702</v>
       </c>
       <c r="E3" s="1">
-        <v>6000</v>
-      </c>
-      <c r="F3" s="1">
-        <v>6000</v>
-      </c>
-      <c r="G3" s="1">
         <v>4000</v>
       </c>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
       <c r="H3" s="1">
         <f>SUM(D3:G3)</f>
-        <v>23895</v>
+        <v>14702</v>
       </c>
       <c r="I3" s="1">
-        <v>967</v>
-      </c>
-      <c r="J3" s="17"/>
-      <c r="K3" s="1">
-        <v>438</v>
-      </c>
-      <c r="L3" s="1">
-        <v>355</v>
-      </c>
-      <c r="M3" s="1">
-        <v>220</v>
-      </c>
+        <v>493</v>
+      </c>
+      <c r="J3" s="1">
+        <v>455</v>
+      </c>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
       <c r="N3" s="6"/>
-      <c r="O3" s="1">
-        <v>438</v>
-      </c>
-      <c r="P3" s="1">
-        <v>301</v>
-      </c>
-      <c r="Q3" s="1">
-        <v>695</v>
-      </c>
-      <c r="R3" s="1">
-        <v>273</v>
-      </c>
-      <c r="S3" s="1">
-        <v>314</v>
-      </c>
-      <c r="T3" s="1">
-        <v>437</v>
-      </c>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
       <c r="U3" s="6"/>
-      <c r="V3" s="1">
-        <v>179</v>
-      </c>
-      <c r="W3" s="1">
-        <v>864</v>
-      </c>
-      <c r="X3" s="1">
-        <v>182</v>
-      </c>
-      <c r="Y3" s="1">
-        <v>1374</v>
-      </c>
-      <c r="Z3" s="1">
-        <v>275</v>
-      </c>
-      <c r="AA3" s="1">
-        <v>215</v>
-      </c>
+      <c r="V3" s="1"/>
+      <c r="W3" s="1"/>
+      <c r="X3" s="1"/>
+      <c r="Y3" s="1"/>
+      <c r="Z3" s="1"/>
+      <c r="AA3" s="1"/>
       <c r="AB3" s="6"/>
-      <c r="AC3" s="1">
-        <v>72</v>
-      </c>
-      <c r="AD3" s="1">
-        <v>1721</v>
-      </c>
+      <c r="AC3" s="1"/>
+      <c r="AD3" s="1"/>
       <c r="AE3" s="1"/>
       <c r="AF3" s="1"/>
       <c r="AG3" s="1"/>
@@ -878,11 +836,11 @@
       <c r="AL3" s="1"/>
       <c r="AM3" s="2">
         <f>SUM(I3:AL3)</f>
-        <v>9320</v>
+        <v>948</v>
       </c>
       <c r="AN3" s="4">
         <f t="shared" ref="AN3:AN9" si="0">H3-AM3</f>
-        <v>14575</v>
+        <v>13754</v>
       </c>
     </row>
     <row r="4" spans="1:40" x14ac:dyDescent="0.35">
@@ -893,79 +851,43 @@
         <v>70</v>
       </c>
       <c r="D4" s="1">
-        <v>5619</v>
+        <v>11028</v>
       </c>
       <c r="E4" s="1">
-        <v>6000</v>
-      </c>
-      <c r="F4" s="1">
         <v>4000</v>
       </c>
-      <c r="G4" s="1">
-        <v>8000</v>
-      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
       <c r="H4" s="1">
         <f t="shared" ref="H4:H9" si="1">SUM(D4:G4)</f>
-        <v>23619</v>
+        <v>15028</v>
       </c>
       <c r="I4" s="1">
-        <v>888</v>
-      </c>
-      <c r="J4" s="17"/>
-      <c r="K4" s="1">
-        <v>431</v>
-      </c>
-      <c r="L4" s="1">
-        <v>321</v>
-      </c>
-      <c r="M4" s="1">
-        <v>135</v>
-      </c>
+        <v>420</v>
+      </c>
+      <c r="J4" s="1">
+        <v>337</v>
+      </c>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
       <c r="N4" s="6"/>
-      <c r="O4" s="1">
-        <v>549</v>
-      </c>
-      <c r="P4" s="1">
-        <v>246</v>
-      </c>
-      <c r="Q4" s="1">
-        <v>835</v>
-      </c>
-      <c r="R4" s="1">
-        <v>267</v>
-      </c>
-      <c r="S4" s="1">
-        <v>423</v>
-      </c>
-      <c r="T4" s="1">
-        <v>251</v>
-      </c>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
       <c r="U4" s="6"/>
-      <c r="V4" s="1">
-        <v>217</v>
-      </c>
-      <c r="W4" s="1">
-        <v>669</v>
-      </c>
-      <c r="X4" s="1">
-        <v>126</v>
-      </c>
-      <c r="Y4" s="1">
-        <v>1452</v>
-      </c>
-      <c r="Z4" s="1">
-        <v>328</v>
-      </c>
-      <c r="AA4" s="1">
-        <v>370</v>
-      </c>
+      <c r="V4" s="1"/>
+      <c r="W4" s="1"/>
+      <c r="X4" s="1"/>
+      <c r="Y4" s="1"/>
+      <c r="Z4" s="1"/>
+      <c r="AA4" s="1"/>
       <c r="AB4" s="6"/>
-      <c r="AC4" s="1">
-        <v>75</v>
-      </c>
-      <c r="AD4" s="1">
-        <v>1665</v>
-      </c>
+      <c r="AC4" s="1"/>
+      <c r="AD4" s="1"/>
       <c r="AE4" s="1"/>
       <c r="AF4" s="1"/>
       <c r="AG4" s="1"/>
@@ -976,11 +898,11 @@
       <c r="AL4" s="1"/>
       <c r="AM4" s="2">
         <f t="shared" ref="AM4:AM9" si="2">SUM(I4:AL4)</f>
-        <v>9248</v>
+        <v>757</v>
       </c>
       <c r="AN4" s="4">
         <f t="shared" si="0"/>
-        <v>14371</v>
+        <v>14271</v>
       </c>
     </row>
     <row r="5" spans="1:40" x14ac:dyDescent="0.35">
@@ -991,79 +913,43 @@
         <v>70</v>
       </c>
       <c r="D5" s="1">
-        <v>3200</v>
+        <v>6654</v>
       </c>
       <c r="E5" s="1">
-        <v>6000</v>
-      </c>
-      <c r="F5" s="1">
-        <v>6000</v>
-      </c>
-      <c r="G5" s="1">
-        <v>10000</v>
-      </c>
+        <v>8000</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
       <c r="H5" s="1">
         <f t="shared" si="1"/>
-        <v>25200</v>
+        <v>14654</v>
       </c>
       <c r="I5" s="1">
-        <v>1073</v>
-      </c>
-      <c r="J5" s="17"/>
-      <c r="K5" s="1">
-        <v>495</v>
-      </c>
-      <c r="L5" s="1">
-        <v>377</v>
-      </c>
-      <c r="M5" s="1">
-        <v>240</v>
-      </c>
+        <v>566</v>
+      </c>
+      <c r="J5" s="1">
+        <v>856</v>
+      </c>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
       <c r="N5" s="6"/>
-      <c r="O5" s="1">
-        <v>518</v>
-      </c>
-      <c r="P5" s="1">
-        <v>243</v>
-      </c>
-      <c r="Q5" s="1">
-        <v>1478</v>
-      </c>
-      <c r="R5" s="1">
-        <v>383</v>
-      </c>
-      <c r="S5" s="1">
-        <v>784</v>
-      </c>
-      <c r="T5" s="1">
-        <v>221</v>
-      </c>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1"/>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1"/>
       <c r="U5" s="6"/>
-      <c r="V5" s="1">
-        <v>169</v>
-      </c>
-      <c r="W5" s="1">
-        <v>734</v>
-      </c>
-      <c r="X5" s="1">
-        <v>80</v>
-      </c>
-      <c r="Y5" s="1">
-        <v>2616</v>
-      </c>
-      <c r="Z5" s="1">
-        <v>425</v>
-      </c>
-      <c r="AA5" s="1">
-        <v>699</v>
-      </c>
+      <c r="V5" s="1"/>
+      <c r="W5" s="1"/>
+      <c r="X5" s="1"/>
+      <c r="Y5" s="1"/>
+      <c r="Z5" s="1"/>
+      <c r="AA5" s="1"/>
       <c r="AB5" s="6"/>
-      <c r="AC5" s="1">
-        <v>133</v>
-      </c>
-      <c r="AD5" s="1">
-        <v>2274</v>
-      </c>
+      <c r="AC5" s="1"/>
+      <c r="AD5" s="1"/>
       <c r="AE5" s="1"/>
       <c r="AF5" s="1"/>
       <c r="AG5" s="1"/>
@@ -1074,11 +960,11 @@
       <c r="AL5" s="1"/>
       <c r="AM5" s="2">
         <f t="shared" si="2"/>
-        <v>12942</v>
+        <v>1422</v>
       </c>
       <c r="AN5" s="4">
         <f t="shared" si="0"/>
-        <v>12258</v>
+        <v>13232</v>
       </c>
     </row>
     <row r="6" spans="1:40" x14ac:dyDescent="0.35">
@@ -1089,79 +975,43 @@
         <v>120</v>
       </c>
       <c r="D6" s="1">
-        <v>5460</v>
+        <v>6228</v>
       </c>
       <c r="E6" s="1">
         <v>6000</v>
       </c>
-      <c r="F6" s="1">
-        <v>6000</v>
-      </c>
-      <c r="G6" s="1">
-        <v>10000</v>
-      </c>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
       <c r="H6" s="1">
         <f t="shared" si="1"/>
-        <v>27460</v>
+        <v>12228</v>
       </c>
       <c r="I6" s="1">
-        <v>921</v>
-      </c>
-      <c r="J6" s="17"/>
-      <c r="K6" s="1">
-        <v>975</v>
-      </c>
-      <c r="L6" s="1">
-        <v>512</v>
-      </c>
-      <c r="M6" s="1">
-        <v>493</v>
-      </c>
+        <v>543</v>
+      </c>
+      <c r="J6" s="1">
+        <v>732</v>
+      </c>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
       <c r="N6" s="6"/>
-      <c r="O6" s="1">
-        <v>1104</v>
-      </c>
-      <c r="P6" s="1">
-        <v>718</v>
-      </c>
-      <c r="Q6" s="1">
-        <v>1828</v>
-      </c>
-      <c r="R6" s="1">
-        <v>382</v>
-      </c>
-      <c r="S6" s="1">
-        <v>703</v>
-      </c>
-      <c r="T6" s="1">
-        <v>1166</v>
-      </c>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
       <c r="U6" s="6"/>
-      <c r="V6" s="1">
-        <v>340</v>
-      </c>
-      <c r="W6" s="1">
-        <v>676</v>
-      </c>
-      <c r="X6" s="1">
-        <v>292</v>
-      </c>
-      <c r="Y6" s="1">
-        <v>2702</v>
-      </c>
-      <c r="Z6" s="1">
-        <v>726</v>
-      </c>
-      <c r="AA6" s="1">
-        <v>623</v>
-      </c>
+      <c r="V6" s="1"/>
+      <c r="W6" s="1"/>
+      <c r="X6" s="1"/>
+      <c r="Y6" s="1"/>
+      <c r="Z6" s="1"/>
+      <c r="AA6" s="1"/>
       <c r="AB6" s="6"/>
-      <c r="AC6" s="1">
-        <v>254</v>
-      </c>
-      <c r="AD6" s="1">
-        <v>2070</v>
-      </c>
+      <c r="AC6" s="1"/>
+      <c r="AD6" s="1"/>
       <c r="AE6" s="1"/>
       <c r="AF6" s="1"/>
       <c r="AG6" s="1"/>
@@ -1172,11 +1022,11 @@
       <c r="AL6" s="1"/>
       <c r="AM6" s="2">
         <f t="shared" si="2"/>
-        <v>16485</v>
+        <v>1275</v>
       </c>
       <c r="AN6" s="4">
         <f t="shared" si="0"/>
-        <v>10975</v>
+        <v>10953</v>
       </c>
     </row>
     <row r="7" spans="1:40" x14ac:dyDescent="0.35">
@@ -1187,79 +1037,43 @@
         <v>120</v>
       </c>
       <c r="D7" s="1">
-        <v>7709</v>
+        <v>2954</v>
       </c>
       <c r="E7" s="1">
-        <v>6000</v>
-      </c>
-      <c r="F7" s="1">
-        <v>4000</v>
-      </c>
-      <c r="G7" s="1">
-        <v>6000</v>
-      </c>
+        <v>10000</v>
+      </c>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
       <c r="H7" s="1">
         <f t="shared" si="1"/>
-        <v>23709</v>
+        <v>12954</v>
       </c>
       <c r="I7" s="1">
-        <v>876</v>
-      </c>
-      <c r="J7" s="17"/>
-      <c r="K7" s="1">
-        <v>892</v>
-      </c>
-      <c r="L7" s="1">
-        <v>440</v>
-      </c>
-      <c r="M7" s="1">
-        <v>381</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="J7" s="1">
+        <v>705</v>
+      </c>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
       <c r="N7" s="6"/>
-      <c r="O7" s="1">
-        <v>1476</v>
-      </c>
-      <c r="P7" s="1">
-        <v>457</v>
-      </c>
-      <c r="Q7" s="1">
-        <v>2050</v>
-      </c>
-      <c r="R7" s="1">
-        <v>323</v>
-      </c>
-      <c r="S7" s="1">
-        <v>714</v>
-      </c>
-      <c r="T7" s="1">
-        <v>768</v>
-      </c>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
       <c r="U7" s="6"/>
-      <c r="V7" s="1">
-        <v>285</v>
-      </c>
-      <c r="W7" s="1">
-        <v>765</v>
-      </c>
-      <c r="X7" s="1">
-        <v>266</v>
-      </c>
-      <c r="Y7" s="1">
-        <v>1487</v>
-      </c>
-      <c r="Z7" s="1">
-        <v>549</v>
-      </c>
-      <c r="AA7" s="1">
-        <v>612</v>
-      </c>
+      <c r="V7" s="1"/>
+      <c r="W7" s="1"/>
+      <c r="X7" s="1"/>
+      <c r="Y7" s="1"/>
+      <c r="Z7" s="1"/>
+      <c r="AA7" s="1"/>
       <c r="AB7" s="6"/>
-      <c r="AC7" s="1">
-        <v>198</v>
-      </c>
-      <c r="AD7" s="1">
-        <v>1895</v>
-      </c>
+      <c r="AC7" s="1"/>
+      <c r="AD7" s="1"/>
       <c r="AE7" s="1"/>
       <c r="AF7" s="1"/>
       <c r="AG7" s="1"/>
@@ -1270,11 +1084,11 @@
       <c r="AL7" s="1"/>
       <c r="AM7" s="2">
         <f t="shared" si="2"/>
-        <v>14434</v>
+        <v>1116</v>
       </c>
       <c r="AN7" s="4">
         <f t="shared" si="0"/>
-        <v>9275</v>
+        <v>11838</v>
       </c>
     </row>
     <row r="8" spans="1:40" x14ac:dyDescent="0.35">
@@ -1285,79 +1099,43 @@
         <v>120</v>
       </c>
       <c r="D8" s="1">
-        <v>3180</v>
+        <v>6270</v>
       </c>
       <c r="E8" s="1">
-        <v>12000</v>
-      </c>
-      <c r="F8" s="1">
-        <v>14000</v>
-      </c>
-      <c r="G8" s="1">
         <v>8000</v>
       </c>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
       <c r="H8" s="1">
         <f t="shared" si="1"/>
-        <v>37180</v>
+        <v>14270</v>
       </c>
       <c r="I8" s="1">
-        <v>882</v>
-      </c>
-      <c r="J8" s="17"/>
-      <c r="K8" s="1">
-        <v>655</v>
-      </c>
-      <c r="L8" s="1">
-        <v>117</v>
-      </c>
-      <c r="M8" s="1">
-        <v>570</v>
-      </c>
+        <v>606</v>
+      </c>
+      <c r="J8" s="1">
+        <v>1027</v>
+      </c>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
       <c r="N8" s="6"/>
-      <c r="O8" s="1">
-        <v>2189</v>
-      </c>
-      <c r="P8" s="1">
-        <v>781</v>
-      </c>
-      <c r="Q8" s="1">
-        <v>3306</v>
-      </c>
-      <c r="R8" s="1">
-        <v>595</v>
-      </c>
-      <c r="S8" s="1">
-        <v>1517</v>
-      </c>
-      <c r="T8" s="1">
-        <v>1134</v>
-      </c>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1"/>
       <c r="U8" s="6"/>
-      <c r="V8" s="1">
-        <v>291</v>
-      </c>
-      <c r="W8" s="1">
-        <v>646</v>
-      </c>
-      <c r="X8" s="1">
-        <v>328</v>
-      </c>
-      <c r="Y8" s="1">
-        <v>2988</v>
-      </c>
-      <c r="Z8" s="1">
-        <v>515</v>
-      </c>
-      <c r="AA8" s="1">
-        <v>1469</v>
-      </c>
+      <c r="V8" s="1"/>
+      <c r="W8" s="1"/>
+      <c r="X8" s="1"/>
+      <c r="Y8" s="1"/>
+      <c r="Z8" s="1"/>
+      <c r="AA8" s="1"/>
       <c r="AB8" s="6"/>
-      <c r="AC8" s="1">
-        <v>244</v>
-      </c>
-      <c r="AD8" s="1">
-        <v>2934</v>
-      </c>
+      <c r="AC8" s="1"/>
+      <c r="AD8" s="1"/>
       <c r="AE8" s="1"/>
       <c r="AF8" s="1"/>
       <c r="AG8" s="1"/>
@@ -1368,11 +1146,11 @@
       <c r="AL8" s="1"/>
       <c r="AM8" s="2">
         <f t="shared" si="2"/>
-        <v>21161</v>
+        <v>1633</v>
       </c>
       <c r="AN8" s="4">
         <f t="shared" si="0"/>
-        <v>16019</v>
+        <v>12637</v>
       </c>
     </row>
     <row r="9" spans="1:40" x14ac:dyDescent="0.35">
@@ -1383,63 +1161,33 @@
         <v>60</v>
       </c>
       <c r="D9" s="1">
-        <v>15644</v>
+        <v>8</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9" s="1">
         <f t="shared" si="1"/>
-        <v>15644</v>
-      </c>
-      <c r="I9" s="1">
-        <v>320</v>
-      </c>
-      <c r="J9" s="17"/>
-      <c r="K9" s="1">
-        <v>1283</v>
-      </c>
-      <c r="L9" s="1">
-        <v>506</v>
-      </c>
-      <c r="M9" s="1">
-        <v>436</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
       <c r="N9" s="6"/>
-      <c r="O9" s="1">
-        <v>2168</v>
-      </c>
-      <c r="P9" s="1">
-        <v>651</v>
-      </c>
-      <c r="Q9" s="1">
-        <v>324</v>
-      </c>
-      <c r="R9" s="1">
-        <v>755</v>
-      </c>
-      <c r="S9" s="1">
-        <v>232</v>
-      </c>
-      <c r="T9" s="1">
-        <v>392</v>
-      </c>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
       <c r="U9" s="6"/>
-      <c r="V9" s="1">
-        <v>206</v>
-      </c>
-      <c r="W9" s="1">
-        <v>737</v>
-      </c>
-      <c r="X9" s="1">
-        <v>541</v>
-      </c>
-      <c r="Y9" s="1">
-        <v>469</v>
-      </c>
-      <c r="Z9" s="1">
-        <v>40</v>
-      </c>
+      <c r="V9" s="1"/>
+      <c r="W9" s="1"/>
+      <c r="X9" s="1"/>
+      <c r="Y9" s="1"/>
+      <c r="Z9" s="1"/>
       <c r="AA9" s="1"/>
       <c r="AB9" s="6"/>
       <c r="AC9" s="1"/>
@@ -1454,11 +1202,11 @@
       <c r="AL9" s="1"/>
       <c r="AM9" s="2">
         <f t="shared" si="2"/>
-        <v>9060</v>
+        <v>0</v>
       </c>
       <c r="AN9" s="4">
         <f t="shared" si="0"/>
-        <v>6584</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1468,43 +1216,43 @@
       <c r="C10" s="1"/>
       <c r="D10" s="5">
         <f>SUM(D3:D9)</f>
-        <v>48707</v>
+        <v>43844</v>
       </c>
       <c r="E10" s="5">
         <f>SUM(E3:E9)</f>
-        <v>42000</v>
+        <v>40000</v>
       </c>
       <c r="F10" s="5">
         <f>SUM(F3:F9)</f>
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="G10" s="5">
         <f>SUM(G3:G9)</f>
-        <v>46000</v>
+        <v>0</v>
       </c>
       <c r="H10" s="5">
         <f>SUM(H3:H9)</f>
-        <v>176707</v>
+        <v>83844</v>
       </c>
       <c r="I10" s="5">
         <f t="shared" ref="I10:AN10" si="3">SUM(I3:I9)</f>
-        <v>5927</v>
+        <v>3039</v>
       </c>
       <c r="J10" s="5">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4112</v>
       </c>
       <c r="K10" s="5">
         <f t="shared" si="3"/>
-        <v>5169</v>
+        <v>0</v>
       </c>
       <c r="L10" s="5">
         <f t="shared" si="3"/>
-        <v>2628</v>
+        <v>0</v>
       </c>
       <c r="M10" s="5">
         <f t="shared" si="3"/>
-        <v>2475</v>
+        <v>0</v>
       </c>
       <c r="N10" s="5">
         <f t="shared" si="3"/>
@@ -1512,27 +1260,27 @@
       </c>
       <c r="O10" s="5">
         <f t="shared" si="3"/>
-        <v>8442</v>
+        <v>0</v>
       </c>
       <c r="P10" s="5">
         <f t="shared" si="3"/>
-        <v>3397</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="5">
         <f t="shared" si="3"/>
-        <v>10516</v>
+        <v>0</v>
       </c>
       <c r="R10" s="5">
         <f t="shared" si="3"/>
-        <v>2978</v>
+        <v>0</v>
       </c>
       <c r="S10" s="5">
         <f t="shared" si="3"/>
-        <v>4687</v>
+        <v>0</v>
       </c>
       <c r="T10" s="5">
         <f t="shared" si="3"/>
-        <v>4369</v>
+        <v>0</v>
       </c>
       <c r="U10" s="5">
         <f t="shared" si="3"/>
@@ -1540,27 +1288,27 @@
       </c>
       <c r="V10" s="5">
         <f t="shared" si="3"/>
-        <v>1687</v>
+        <v>0</v>
       </c>
       <c r="W10" s="5">
         <f t="shared" si="3"/>
-        <v>5091</v>
+        <v>0</v>
       </c>
       <c r="X10" s="5">
         <f t="shared" si="3"/>
-        <v>1815</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="5">
         <f t="shared" si="3"/>
-        <v>13088</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="5">
         <f t="shared" si="3"/>
-        <v>2858</v>
+        <v>0</v>
       </c>
       <c r="AA10" s="5">
         <f t="shared" si="3"/>
-        <v>3988</v>
+        <v>0</v>
       </c>
       <c r="AB10" s="5">
         <f t="shared" si="3"/>
@@ -1568,11 +1316,11 @@
       </c>
       <c r="AC10" s="5">
         <f t="shared" si="3"/>
-        <v>976</v>
+        <v>0</v>
       </c>
       <c r="AD10" s="5">
         <f t="shared" si="3"/>
-        <v>12559</v>
+        <v>0</v>
       </c>
       <c r="AE10" s="5">
         <f t="shared" si="3"/>
@@ -1608,11 +1356,11 @@
       </c>
       <c r="AM10" s="5">
         <f t="shared" si="3"/>
-        <v>92650</v>
+        <v>7151</v>
       </c>
       <c r="AN10" s="5">
         <f t="shared" si="3"/>
-        <v>84057</v>
+        <v>76693</v>
       </c>
     </row>
     <row r="11" spans="1:40" ht="19" customHeight="1" x14ac:dyDescent="0.35">
@@ -1622,43 +1370,43 @@
       <c r="C11" s="1"/>
       <c r="D11" s="5">
         <f>D10/40</f>
-        <v>1217.675</v>
+        <v>1096.0999999999999</v>
       </c>
       <c r="E11" s="5">
         <f>E10/40</f>
-        <v>1050</v>
+        <v>1000</v>
       </c>
       <c r="F11" s="5">
         <f>F10/40</f>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <f>G10/40</f>
-        <v>1150</v>
+        <v>0</v>
       </c>
       <c r="H11" s="15">
         <f>H10/40</f>
-        <v>4417.6750000000002</v>
+        <v>2096.1</v>
       </c>
       <c r="I11" s="5">
         <f t="shared" ref="I11:AN11" si="4">I10/40</f>
-        <v>148.17500000000001</v>
+        <v>75.974999999999994</v>
       </c>
       <c r="J11" s="5">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>102.8</v>
       </c>
       <c r="K11" s="5">
         <f t="shared" si="4"/>
-        <v>129.22499999999999</v>
+        <v>0</v>
       </c>
       <c r="L11" s="5">
         <f t="shared" si="4"/>
-        <v>65.7</v>
+        <v>0</v>
       </c>
       <c r="M11" s="5">
         <f t="shared" si="4"/>
-        <v>61.875</v>
+        <v>0</v>
       </c>
       <c r="N11" s="5">
         <f t="shared" si="4"/>
@@ -1666,27 +1414,27 @@
       </c>
       <c r="O11" s="5">
         <f t="shared" si="4"/>
-        <v>211.05</v>
+        <v>0</v>
       </c>
       <c r="P11" s="5">
         <f t="shared" si="4"/>
-        <v>84.924999999999997</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="5">
         <f t="shared" si="4"/>
-        <v>262.89999999999998</v>
+        <v>0</v>
       </c>
       <c r="R11" s="5">
         <f t="shared" si="4"/>
-        <v>74.45</v>
+        <v>0</v>
       </c>
       <c r="S11" s="5">
         <f t="shared" si="4"/>
-        <v>117.175</v>
+        <v>0</v>
       </c>
       <c r="T11" s="5">
         <f t="shared" si="4"/>
-        <v>109.22499999999999</v>
+        <v>0</v>
       </c>
       <c r="U11" s="5">
         <f t="shared" si="4"/>
@@ -1694,27 +1442,27 @@
       </c>
       <c r="V11" s="5">
         <f t="shared" si="4"/>
-        <v>42.174999999999997</v>
+        <v>0</v>
       </c>
       <c r="W11" s="5">
         <f t="shared" si="4"/>
-        <v>127.27500000000001</v>
+        <v>0</v>
       </c>
       <c r="X11" s="5">
         <f t="shared" si="4"/>
-        <v>45.375</v>
+        <v>0</v>
       </c>
       <c r="Y11" s="5">
         <f t="shared" si="4"/>
-        <v>327.2</v>
+        <v>0</v>
       </c>
       <c r="Z11" s="5">
         <f t="shared" si="4"/>
-        <v>71.45</v>
+        <v>0</v>
       </c>
       <c r="AA11" s="5">
         <f t="shared" si="4"/>
-        <v>99.7</v>
+        <v>0</v>
       </c>
       <c r="AB11" s="5">
         <f t="shared" si="4"/>
@@ -1722,11 +1470,11 @@
       </c>
       <c r="AC11" s="5">
         <f t="shared" si="4"/>
-        <v>24.4</v>
+        <v>0</v>
       </c>
       <c r="AD11" s="5">
         <f t="shared" si="4"/>
-        <v>313.97500000000002</v>
+        <v>0</v>
       </c>
       <c r="AE11" s="5">
         <f t="shared" si="4"/>
@@ -1762,25 +1510,25 @@
       </c>
       <c r="AM11" s="15">
         <f t="shared" si="4"/>
-        <v>2316.25</v>
+        <v>178.77500000000001</v>
       </c>
       <c r="AN11" s="16">
         <f t="shared" si="4"/>
-        <v>2101.4250000000002</v>
+        <v>1917.325</v>
       </c>
     </row>
     <row r="12" spans="1:40" x14ac:dyDescent="0.35">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="20"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
       <c r="E12" s="12"/>
       <c r="F12" s="12"/>
       <c r="G12" s="12"/>
       <c r="H12" s="12"/>
-      <c r="M12" s="18"/>
+      <c r="M12" s="17"/>
     </row>
     <row r="13" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">

--- a/OCT_2026/Reports/Monthly.xlsx
+++ b/OCT_2026/Reports/Monthly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC69D6E9-EA49-4EF9-8277-033BF1D51500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{528AF34A-56D0-48E5-AF9F-9E66B54D1019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{3E645682-E893-4F6E-94AA-185947CE66D6}"/>
   </bookViews>

--- a/OCT_2026/Reports/Monthly.xlsx
+++ b/OCT_2026/Reports/Monthly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\OCT_2026\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{528AF34A-56D0-48E5-AF9F-9E66B54D1019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{544BFCAA-53A0-422C-8204-BD655B45F138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{3E645682-E893-4F6E-94AA-185947CE66D6}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t xml:space="preserve">Opening </t>
   </si>
@@ -94,13 +94,25 @@
   </si>
   <si>
     <t>OCT</t>
+  </si>
+  <si>
+    <t>Chicken Promo 4 in 1</t>
+  </si>
+  <si>
+    <t>Meat 70.</t>
+  </si>
+  <si>
+    <t>Chk 120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Promo </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -128,6 +140,29 @@
       <b/>
       <sz val="18"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1" tint="0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1" tint="0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1" tint="0.249977111117893"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -212,7 +247,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -261,6 +296,29 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -577,7 +635,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3DC3771-1E8D-4C4A-A561-EB9042DCC7D5}">
-  <dimension ref="A1:AN76"/>
+  <dimension ref="A1:AO77"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.6328125" customWidth="1"/>
@@ -585,38 +643,39 @@
     <col min="3" max="3" width="5.26953125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.7265625" customWidth="1"/>
     <col min="5" max="5" width="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="8.7265625" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="8.7265625" customWidth="1"/>
-    <col min="9" max="9" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.6328125" customWidth="1"/>
-    <col min="11" max="11" width="5.81640625" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="6.26953125" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="7.36328125" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="2.453125" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="6.90625" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="9.453125" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="7.1796875" hidden="1" customWidth="1"/>
-    <col min="18" max="20" width="9.453125" hidden="1" customWidth="1"/>
-    <col min="21" max="21" width="2.90625" hidden="1" customWidth="1"/>
-    <col min="22" max="22" width="8.26953125" hidden="1" customWidth="1"/>
-    <col min="23" max="23" width="9.453125" hidden="1" customWidth="1"/>
-    <col min="24" max="24" width="7.81640625" hidden="1" customWidth="1"/>
-    <col min="25" max="27" width="9.453125" hidden="1" customWidth="1"/>
-    <col min="28" max="28" width="3.08984375" hidden="1" customWidth="1"/>
-    <col min="29" max="29" width="8.6328125" hidden="1" customWidth="1"/>
-    <col min="30" max="30" width="7" hidden="1" customWidth="1"/>
-    <col min="31" max="31" width="6.1796875" hidden="1" customWidth="1"/>
-    <col min="32" max="32" width="7.54296875" hidden="1" customWidth="1"/>
-    <col min="33" max="33" width="6.453125" hidden="1" customWidth="1"/>
-    <col min="34" max="34" width="7.453125" hidden="1" customWidth="1"/>
-    <col min="35" max="35" width="8.6328125" hidden="1" customWidth="1"/>
-    <col min="36" max="36" width="6.453125" hidden="1" customWidth="1"/>
-    <col min="37" max="37" width="8.6328125" hidden="1" customWidth="1"/>
-    <col min="38" max="38" width="7.54296875" hidden="1" customWidth="1"/>
-    <col min="39" max="39" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="8.7265625" customWidth="1"/>
+    <col min="10" max="10" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.6328125" customWidth="1"/>
+    <col min="12" max="12" width="5.81640625" customWidth="1"/>
+    <col min="13" max="13" width="2.453125" customWidth="1"/>
+    <col min="14" max="14" width="7.36328125" customWidth="1"/>
+    <col min="15" max="16" width="6.90625" customWidth="1"/>
+    <col min="17" max="17" width="9.453125" customWidth="1"/>
+    <col min="18" max="18" width="7.1796875" customWidth="1"/>
+    <col min="19" max="19" width="9.453125" customWidth="1"/>
+    <col min="20" max="20" width="3.08984375" customWidth="1"/>
+    <col min="21" max="22" width="9.453125" customWidth="1"/>
+    <col min="23" max="23" width="8.26953125" customWidth="1"/>
+    <col min="24" max="24" width="3.26953125" customWidth="1"/>
+    <col min="25" max="25" width="7.81640625" customWidth="1"/>
+    <col min="26" max="26" width="9.453125" customWidth="1"/>
+    <col min="27" max="27" width="3.26953125" customWidth="1"/>
+    <col min="28" max="28" width="9.453125" customWidth="1"/>
+    <col min="29" max="29" width="6.54296875" customWidth="1"/>
+    <col min="30" max="30" width="8.6328125" customWidth="1"/>
+    <col min="31" max="31" width="7" customWidth="1"/>
+    <col min="32" max="32" width="6.1796875" customWidth="1"/>
+    <col min="33" max="33" width="7.54296875" customWidth="1"/>
+    <col min="34" max="34" width="3.08984375" customWidth="1"/>
+    <col min="35" max="35" width="7.453125" customWidth="1"/>
+    <col min="36" max="36" width="8.6328125" customWidth="1"/>
+    <col min="37" max="37" width="6.453125" customWidth="1"/>
+    <col min="38" max="38" width="8.6328125" customWidth="1"/>
+    <col min="39" max="39" width="7.54296875" customWidth="1"/>
+    <col min="40" max="40" width="9.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" ht="36.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:41" ht="36.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
         <v>22</v>
       </c>
@@ -661,8 +720,9 @@
       <c r="AL1" s="18"/>
       <c r="AM1" s="18"/>
       <c r="AN1" s="18"/>
-    </row>
-    <row r="2" spans="1:40" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AO1" s="18"/>
+    </row>
+    <row r="2" spans="1:41" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
@@ -676,987 +736,1360 @@
         <v>46296</v>
       </c>
       <c r="F2" s="14">
-        <v>46296</v>
+        <v>289</v>
       </c>
       <c r="G2" s="14">
-        <v>46296</v>
-      </c>
-      <c r="H2" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="H2" s="14">
+        <v>46324</v>
+      </c>
+      <c r="I2" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="9">
+      <c r="J2" s="9">
         <v>1</v>
       </c>
-      <c r="J2" s="9">
+      <c r="K2" s="9">
         <v>2</v>
       </c>
-      <c r="K2" s="9">
+      <c r="L2" s="9">
         <v>3</v>
       </c>
-      <c r="L2" s="9">
+      <c r="M2" s="22">
         <v>4</v>
       </c>
-      <c r="M2" s="9">
+      <c r="N2" s="9">
         <v>5</v>
       </c>
-      <c r="N2" s="9">
+      <c r="O2" s="9">
         <v>6</v>
       </c>
-      <c r="O2" s="9">
+      <c r="P2" s="9">
         <v>7</v>
       </c>
-      <c r="P2" s="9">
+      <c r="Q2" s="9">
         <v>8</v>
       </c>
-      <c r="Q2" s="9">
+      <c r="R2" s="9">
         <v>9</v>
       </c>
-      <c r="R2" s="9">
+      <c r="S2" s="9">
         <v>10</v>
       </c>
-      <c r="S2" s="9">
+      <c r="T2" s="27">
         <v>11</v>
       </c>
-      <c r="T2" s="9">
+      <c r="U2" s="9">
         <v>12</v>
       </c>
-      <c r="U2" s="9">
+      <c r="V2" s="9">
         <v>13</v>
       </c>
-      <c r="V2" s="9">
+      <c r="W2" s="9">
         <v>14</v>
       </c>
-      <c r="W2" s="9">
+      <c r="X2" s="27">
         <v>15</v>
       </c>
-      <c r="X2" s="9">
+      <c r="Y2" s="9">
         <v>16</v>
       </c>
-      <c r="Y2" s="9">
+      <c r="Z2" s="9">
         <v>17</v>
       </c>
-      <c r="Z2" s="9">
+      <c r="AA2" s="27">
         <v>18</v>
       </c>
-      <c r="AA2" s="9">
+      <c r="AB2" s="9">
         <v>19</v>
       </c>
-      <c r="AB2" s="9">
+      <c r="AC2" s="9">
         <v>20</v>
       </c>
-      <c r="AC2" s="9">
+      <c r="AD2" s="9">
         <v>21</v>
       </c>
-      <c r="AD2" s="9">
+      <c r="AE2" s="9">
         <v>22</v>
       </c>
-      <c r="AE2" s="9">
+      <c r="AF2" s="9">
         <v>23</v>
       </c>
-      <c r="AF2" s="9">
+      <c r="AG2" s="9">
         <v>24</v>
       </c>
-      <c r="AG2" s="9">
+      <c r="AH2" s="27">
         <v>25</v>
       </c>
-      <c r="AH2" s="9">
+      <c r="AI2" s="9">
         <v>26</v>
       </c>
-      <c r="AI2" s="9">
+      <c r="AJ2" s="9">
         <v>27</v>
       </c>
-      <c r="AJ2" s="9">
+      <c r="AK2" s="9">
         <v>28</v>
       </c>
-      <c r="AK2" s="9">
+      <c r="AL2" s="9">
         <v>29</v>
       </c>
-      <c r="AL2" s="9">
+      <c r="AM2" s="9">
         <v>30</v>
       </c>
-      <c r="AM2" s="10" t="s">
+      <c r="AN2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="AN2" s="11" t="s">
+      <c r="AO2" s="11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:41" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="2">
         <v>70</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="21">
         <v>10702</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="2">
         <v>4000</v>
       </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1">
-        <f>SUM(D3:G3)</f>
-        <v>14702</v>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2">
+        <v>10000</v>
       </c>
       <c r="I3" s="1">
+        <f>SUM(D3:H3)</f>
+        <v>24702</v>
+      </c>
+      <c r="J3" s="1">
         <v>493</v>
       </c>
-      <c r="J3" s="1">
+      <c r="K3" s="1">
         <v>455</v>
       </c>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="1"/>
-      <c r="P3" s="1"/>
-      <c r="Q3" s="1"/>
-      <c r="R3" s="1"/>
-      <c r="S3" s="1"/>
-      <c r="T3" s="1"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="1"/>
-      <c r="W3" s="1"/>
-      <c r="X3" s="1"/>
-      <c r="Y3" s="1"/>
-      <c r="Z3" s="1"/>
-      <c r="AA3" s="1"/>
-      <c r="AB3" s="6"/>
-      <c r="AC3" s="1"/>
-      <c r="AD3" s="1"/>
-      <c r="AE3" s="1"/>
-      <c r="AF3" s="1"/>
-      <c r="AG3" s="1"/>
-      <c r="AH3" s="1"/>
-      <c r="AI3" s="1"/>
-      <c r="AJ3" s="1"/>
-      <c r="AK3" s="1"/>
+      <c r="L3" s="1">
+        <v>520</v>
+      </c>
+      <c r="M3" s="23"/>
+      <c r="N3" s="1">
+        <v>120</v>
+      </c>
+      <c r="O3" s="25">
+        <v>272</v>
+      </c>
+      <c r="P3" s="1">
+        <v>675</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>478</v>
+      </c>
+      <c r="R3" s="1">
+        <v>317</v>
+      </c>
+      <c r="S3" s="1">
+        <v>518</v>
+      </c>
+      <c r="T3" s="6"/>
+      <c r="U3" s="1">
+        <v>1270</v>
+      </c>
+      <c r="V3" s="25">
+        <v>175</v>
+      </c>
+      <c r="W3" s="1">
+        <v>127</v>
+      </c>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="1">
+        <v>894</v>
+      </c>
+      <c r="Z3" s="1">
+        <v>679</v>
+      </c>
+      <c r="AA3" s="6"/>
+      <c r="AB3" s="1">
+        <v>553</v>
+      </c>
+      <c r="AC3" s="25">
+        <v>242</v>
+      </c>
+      <c r="AD3" s="1">
+        <v>889</v>
+      </c>
+      <c r="AE3" s="1">
+        <v>1437</v>
+      </c>
+      <c r="AF3" s="1">
+        <v>466</v>
+      </c>
+      <c r="AG3" s="1">
+        <v>376</v>
+      </c>
+      <c r="AH3" s="6"/>
+      <c r="AI3" s="1">
+        <v>276</v>
+      </c>
+      <c r="AJ3" s="1">
+        <v>386</v>
+      </c>
+      <c r="AK3" s="1">
+        <v>426</v>
+      </c>
       <c r="AL3" s="1"/>
-      <c r="AM3" s="2">
-        <f>SUM(I3:AL3)</f>
-        <v>948</v>
-      </c>
-      <c r="AN3" s="4">
-        <f t="shared" ref="AN3:AN9" si="0">H3-AM3</f>
-        <v>13754</v>
-      </c>
-    </row>
-    <row r="4" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="AM3" s="1"/>
+      <c r="AN3" s="2">
+        <f>SUM(J3:AM3)</f>
+        <v>12044</v>
+      </c>
+      <c r="AO3" s="4">
+        <f t="shared" ref="AO3:AO10" si="0">I3-AN3</f>
+        <v>12658</v>
+      </c>
+    </row>
+    <row r="4" spans="1:41" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="2">
         <v>70</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="21">
         <v>11028</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="2">
         <v>4000</v>
       </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1">
-        <f t="shared" ref="H4:H9" si="1">SUM(D4:G4)</f>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="1">
+        <f>SUM(D4:H4)</f>
         <v>15028</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4" s="1">
         <v>420</v>
       </c>
-      <c r="J4" s="1">
+      <c r="K4" s="1">
         <v>337</v>
       </c>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="1"/>
-      <c r="R4" s="1"/>
-      <c r="S4" s="1"/>
-      <c r="T4" s="1"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="1"/>
-      <c r="W4" s="1"/>
-      <c r="X4" s="1"/>
-      <c r="Y4" s="1"/>
-      <c r="Z4" s="1"/>
-      <c r="AA4" s="1"/>
-      <c r="AB4" s="6"/>
-      <c r="AC4" s="1"/>
-      <c r="AD4" s="1"/>
-      <c r="AE4" s="1"/>
-      <c r="AF4" s="1"/>
-      <c r="AG4" s="1"/>
-      <c r="AH4" s="1"/>
-      <c r="AI4" s="1"/>
-      <c r="AJ4" s="1"/>
-      <c r="AK4" s="1"/>
+      <c r="L4" s="1">
+        <v>383</v>
+      </c>
+      <c r="M4" s="23"/>
+      <c r="N4" s="1">
+        <v>90</v>
+      </c>
+      <c r="O4" s="25">
+        <v>292</v>
+      </c>
+      <c r="P4" s="1">
+        <v>716</v>
+      </c>
+      <c r="Q4" s="1">
+        <v>599</v>
+      </c>
+      <c r="R4" s="1">
+        <v>180</v>
+      </c>
+      <c r="S4" s="1">
+        <v>611</v>
+      </c>
+      <c r="T4" s="6"/>
+      <c r="U4" s="1">
+        <v>693</v>
+      </c>
+      <c r="V4" s="25">
+        <v>118</v>
+      </c>
+      <c r="W4" s="1">
+        <v>69</v>
+      </c>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="1">
+        <v>883</v>
+      </c>
+      <c r="Z4" s="1">
+        <v>794</v>
+      </c>
+      <c r="AA4" s="6"/>
+      <c r="AB4" s="1">
+        <v>393</v>
+      </c>
+      <c r="AC4" s="25">
+        <v>161</v>
+      </c>
+      <c r="AD4" s="1">
+        <v>730</v>
+      </c>
+      <c r="AE4" s="1">
+        <v>1363</v>
+      </c>
+      <c r="AF4" s="1">
+        <v>508</v>
+      </c>
+      <c r="AG4" s="1">
+        <v>822</v>
+      </c>
+      <c r="AH4" s="6"/>
+      <c r="AI4" s="1">
+        <v>276</v>
+      </c>
+      <c r="AJ4" s="1">
+        <v>405</v>
+      </c>
+      <c r="AK4" s="1">
+        <v>451</v>
+      </c>
       <c r="AL4" s="1"/>
-      <c r="AM4" s="2">
-        <f t="shared" ref="AM4:AM9" si="2">SUM(I4:AL4)</f>
-        <v>757</v>
-      </c>
-      <c r="AN4" s="4">
+      <c r="AM4" s="1"/>
+      <c r="AN4" s="2">
+        <f t="shared" ref="AN4:AN10" si="1">SUM(J4:AM4)</f>
+        <v>11294</v>
+      </c>
+      <c r="AO4" s="4">
         <f t="shared" si="0"/>
-        <v>14271</v>
-      </c>
-    </row>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.35">
+        <v>3734</v>
+      </c>
+    </row>
+    <row r="5" spans="1:41" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="2">
         <v>70</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="21">
         <v>6654</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="2">
         <v>8000</v>
       </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1">
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="1">
+        <f>SUM(D5:H5)</f>
+        <v>14654</v>
+      </c>
+      <c r="J5" s="1">
+        <v>566</v>
+      </c>
+      <c r="K5" s="1">
+        <v>856</v>
+      </c>
+      <c r="L5" s="1">
+        <v>636</v>
+      </c>
+      <c r="M5" s="23"/>
+      <c r="N5" s="1">
+        <v>122</v>
+      </c>
+      <c r="O5" s="25">
+        <v>1307</v>
+      </c>
+      <c r="P5" s="1">
+        <v>700</v>
+      </c>
+      <c r="Q5" s="1">
+        <v>632</v>
+      </c>
+      <c r="R5" s="1">
+        <v>127</v>
+      </c>
+      <c r="S5" s="1">
+        <v>616</v>
+      </c>
+      <c r="T5" s="6"/>
+      <c r="U5" s="1">
+        <v>875</v>
+      </c>
+      <c r="V5" s="25">
+        <v>298</v>
+      </c>
+      <c r="W5" s="1">
+        <v>95</v>
+      </c>
+      <c r="X5" s="6"/>
+      <c r="Y5" s="1">
+        <v>1298</v>
+      </c>
+      <c r="Z5" s="1">
+        <v>955</v>
+      </c>
+      <c r="AA5" s="6"/>
+      <c r="AB5" s="1">
+        <v>1229</v>
+      </c>
+      <c r="AC5" s="25">
+        <v>260</v>
+      </c>
+      <c r="AD5" s="1">
+        <v>1361</v>
+      </c>
+      <c r="AE5" s="1">
+        <v>1355</v>
+      </c>
+      <c r="AF5" s="1">
+        <v>594</v>
+      </c>
+      <c r="AG5" s="1">
+        <v>695</v>
+      </c>
+      <c r="AH5" s="6"/>
+      <c r="AI5" s="1">
+        <v>136</v>
+      </c>
+      <c r="AJ5" s="1">
+        <v>120</v>
+      </c>
+      <c r="AK5" s="1">
+        <v>0</v>
+      </c>
+      <c r="AL5" s="1"/>
+      <c r="AM5" s="1"/>
+      <c r="AN5" s="2">
         <f t="shared" si="1"/>
-        <v>14654</v>
-      </c>
-      <c r="I5" s="1">
-        <v>566</v>
-      </c>
-      <c r="J5" s="1">
-        <v>856</v>
-      </c>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
-      <c r="R5" s="1"/>
-      <c r="S5" s="1"/>
-      <c r="T5" s="1"/>
-      <c r="U5" s="6"/>
-      <c r="V5" s="1"/>
-      <c r="W5" s="1"/>
-      <c r="X5" s="1"/>
-      <c r="Y5" s="1"/>
-      <c r="Z5" s="1"/>
-      <c r="AA5" s="1"/>
-      <c r="AB5" s="6"/>
-      <c r="AC5" s="1"/>
-      <c r="AD5" s="1"/>
-      <c r="AE5" s="1"/>
-      <c r="AF5" s="1"/>
-      <c r="AG5" s="1"/>
-      <c r="AH5" s="1"/>
-      <c r="AI5" s="1"/>
-      <c r="AJ5" s="1"/>
-      <c r="AK5" s="1"/>
-      <c r="AL5" s="1"/>
-      <c r="AM5" s="2">
-        <f t="shared" si="2"/>
-        <v>1422</v>
-      </c>
-      <c r="AN5" s="4">
+        <v>14833</v>
+      </c>
+      <c r="AO5" s="4">
         <f t="shared" si="0"/>
-        <v>13232</v>
-      </c>
-    </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.35">
+        <v>-179</v>
+      </c>
+    </row>
+    <row r="6" spans="1:41" x14ac:dyDescent="0.35">
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="2">
         <v>120</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="21">
         <v>6228</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="2">
         <v>6000</v>
       </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1">
+      <c r="F6" s="2">
+        <v>14000</v>
+      </c>
+      <c r="G6" s="2">
+        <v>400</v>
+      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="1">
+        <f>SUM(D6:H6)</f>
+        <v>26628</v>
+      </c>
+      <c r="J6" s="1">
+        <v>543</v>
+      </c>
+      <c r="K6" s="1">
+        <v>732</v>
+      </c>
+      <c r="L6" s="1">
+        <v>687</v>
+      </c>
+      <c r="M6" s="23"/>
+      <c r="N6" s="1">
+        <v>303</v>
+      </c>
+      <c r="O6" s="25">
+        <v>1394</v>
+      </c>
+      <c r="P6" s="1">
+        <v>1257</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>836</v>
+      </c>
+      <c r="R6" s="1">
+        <v>3591</v>
+      </c>
+      <c r="S6" s="1">
+        <v>657</v>
+      </c>
+      <c r="T6" s="6"/>
+      <c r="U6" s="1">
+        <v>1029</v>
+      </c>
+      <c r="V6" s="25">
+        <v>465</v>
+      </c>
+      <c r="W6" s="1">
+        <v>288</v>
+      </c>
+      <c r="X6" s="6"/>
+      <c r="Y6" s="1">
+        <v>4582</v>
+      </c>
+      <c r="Z6" s="1">
+        <v>1905</v>
+      </c>
+      <c r="AA6" s="6"/>
+      <c r="AB6" s="1">
+        <v>1737</v>
+      </c>
+      <c r="AC6" s="25">
+        <v>651</v>
+      </c>
+      <c r="AD6" s="1">
+        <v>1342</v>
+      </c>
+      <c r="AE6" s="1">
+        <v>1925</v>
+      </c>
+      <c r="AF6" s="1">
+        <v>812</v>
+      </c>
+      <c r="AG6" s="1">
+        <v>1095</v>
+      </c>
+      <c r="AH6" s="6"/>
+      <c r="AI6" s="1">
+        <v>366</v>
+      </c>
+      <c r="AJ6" s="1">
+        <v>682</v>
+      </c>
+      <c r="AK6" s="1">
+        <v>499</v>
+      </c>
+      <c r="AL6" s="1"/>
+      <c r="AM6" s="1"/>
+      <c r="AN6" s="2">
         <f t="shared" si="1"/>
-        <v>12228</v>
-      </c>
-      <c r="I6" s="1">
-        <v>543</v>
-      </c>
-      <c r="J6" s="1">
-        <v>732</v>
-      </c>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
-      <c r="R6" s="1"/>
-      <c r="S6" s="1"/>
-      <c r="T6" s="1"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="1"/>
-      <c r="W6" s="1"/>
-      <c r="X6" s="1"/>
-      <c r="Y6" s="1"/>
-      <c r="Z6" s="1"/>
-      <c r="AA6" s="1"/>
-      <c r="AB6" s="6"/>
-      <c r="AC6" s="1"/>
-      <c r="AD6" s="1"/>
-      <c r="AE6" s="1"/>
-      <c r="AF6" s="1"/>
-      <c r="AG6" s="1"/>
-      <c r="AH6" s="1"/>
-      <c r="AI6" s="1"/>
-      <c r="AJ6" s="1"/>
-      <c r="AK6" s="1"/>
-      <c r="AL6" s="1"/>
-      <c r="AM6" s="2">
-        <f t="shared" si="2"/>
-        <v>1275</v>
-      </c>
-      <c r="AN6" s="4">
+        <v>27378</v>
+      </c>
+      <c r="AO6" s="4">
         <f t="shared" si="0"/>
-        <v>10953</v>
-      </c>
-    </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.35">
+        <v>-750</v>
+      </c>
+    </row>
+    <row r="7" spans="1:41" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2">
         <v>120</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="21">
         <v>2954</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="2">
         <v>10000</v>
       </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1">
+      <c r="F7" s="2">
+        <v>12000</v>
+      </c>
+      <c r="G7" s="2">
+        <v>14000</v>
+      </c>
+      <c r="H7" s="2"/>
+      <c r="I7" s="1">
+        <f>SUM(D7:H7)</f>
+        <v>38954</v>
+      </c>
+      <c r="J7" s="1">
+        <v>411</v>
+      </c>
+      <c r="K7" s="1">
+        <v>705</v>
+      </c>
+      <c r="L7" s="1">
+        <v>535</v>
+      </c>
+      <c r="M7" s="23"/>
+      <c r="N7" s="1">
+        <v>198</v>
+      </c>
+      <c r="O7" s="25">
+        <v>1905</v>
+      </c>
+      <c r="P7" s="1">
+        <v>1562</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>641</v>
+      </c>
+      <c r="R7" s="1">
+        <v>2481</v>
+      </c>
+      <c r="S7" s="1">
+        <v>542</v>
+      </c>
+      <c r="T7" s="6"/>
+      <c r="U7" s="1">
+        <v>1003</v>
+      </c>
+      <c r="V7" s="25">
+        <v>291</v>
+      </c>
+      <c r="W7" s="1">
+        <v>148</v>
+      </c>
+      <c r="X7" s="6"/>
+      <c r="Y7" s="1">
+        <v>3894</v>
+      </c>
+      <c r="Z7" s="1">
+        <v>1928</v>
+      </c>
+      <c r="AA7" s="6"/>
+      <c r="AB7" s="1">
+        <v>1707</v>
+      </c>
+      <c r="AC7" s="25">
+        <v>587</v>
+      </c>
+      <c r="AD7" s="1">
+        <v>1808</v>
+      </c>
+      <c r="AE7" s="1">
+        <v>1660</v>
+      </c>
+      <c r="AF7" s="1">
+        <v>696</v>
+      </c>
+      <c r="AG7" s="1">
+        <v>926</v>
+      </c>
+      <c r="AH7" s="6"/>
+      <c r="AI7" s="1">
+        <v>366</v>
+      </c>
+      <c r="AJ7" s="1">
+        <v>842</v>
+      </c>
+      <c r="AK7" s="1">
+        <v>528</v>
+      </c>
+      <c r="AL7" s="1"/>
+      <c r="AM7" s="1"/>
+      <c r="AN7" s="2">
         <f t="shared" si="1"/>
-        <v>12954</v>
-      </c>
-      <c r="I7" s="1">
-        <v>411</v>
-      </c>
-      <c r="J7" s="1">
-        <v>705</v>
-      </c>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-      <c r="Q7" s="1"/>
-      <c r="R7" s="1"/>
-      <c r="S7" s="1"/>
-      <c r="T7" s="1"/>
-      <c r="U7" s="6"/>
-      <c r="V7" s="1"/>
-      <c r="W7" s="1"/>
-      <c r="X7" s="1"/>
-      <c r="Y7" s="1"/>
-      <c r="Z7" s="1"/>
-      <c r="AA7" s="1"/>
-      <c r="AB7" s="6"/>
-      <c r="AC7" s="1"/>
-      <c r="AD7" s="1"/>
-      <c r="AE7" s="1"/>
-      <c r="AF7" s="1"/>
-      <c r="AG7" s="1"/>
-      <c r="AH7" s="1"/>
-      <c r="AI7" s="1"/>
-      <c r="AJ7" s="1"/>
-      <c r="AK7" s="1"/>
-      <c r="AL7" s="1"/>
-      <c r="AM7" s="2">
-        <f t="shared" si="2"/>
-        <v>1116</v>
-      </c>
-      <c r="AN7" s="4">
+        <v>25364</v>
+      </c>
+      <c r="AO7" s="4">
         <f t="shared" si="0"/>
-        <v>11838</v>
-      </c>
-    </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.35">
+        <v>13590</v>
+      </c>
+    </row>
+    <row r="8" spans="1:41" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="2">
         <v>120</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="21">
         <v>6270</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="2">
         <v>8000</v>
       </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1">
+      <c r="F8" s="2">
+        <v>14000</v>
+      </c>
+      <c r="G8" s="2">
+        <v>20000</v>
+      </c>
+      <c r="H8" s="2">
+        <v>10160</v>
+      </c>
+      <c r="I8" s="1">
+        <f>SUM(D8:H8)</f>
+        <v>58430</v>
+      </c>
+      <c r="J8" s="1">
+        <v>606</v>
+      </c>
+      <c r="K8" s="1">
+        <v>1027</v>
+      </c>
+      <c r="L8" s="1">
+        <v>973</v>
+      </c>
+      <c r="M8" s="23"/>
+      <c r="N8" s="1">
+        <v>354</v>
+      </c>
+      <c r="O8" s="25">
+        <v>1997</v>
+      </c>
+      <c r="P8" s="1">
+        <v>1688</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>829</v>
+      </c>
+      <c r="R8" s="1">
+        <v>4158</v>
+      </c>
+      <c r="S8" s="1">
+        <v>634</v>
+      </c>
+      <c r="T8" s="6"/>
+      <c r="U8" s="1">
+        <v>1212</v>
+      </c>
+      <c r="V8" s="25">
+        <v>340</v>
+      </c>
+      <c r="W8" s="1">
+        <v>291</v>
+      </c>
+      <c r="X8" s="6"/>
+      <c r="Y8" s="1">
+        <v>5156</v>
+      </c>
+      <c r="Z8" s="1">
+        <v>2405</v>
+      </c>
+      <c r="AA8" s="6"/>
+      <c r="AB8" s="1">
+        <v>2348</v>
+      </c>
+      <c r="AC8" s="25">
+        <v>1220</v>
+      </c>
+      <c r="AD8" s="1">
+        <v>2903</v>
+      </c>
+      <c r="AE8" s="1">
+        <v>2018</v>
+      </c>
+      <c r="AF8" s="1">
+        <v>913</v>
+      </c>
+      <c r="AG8" s="1">
+        <v>1157</v>
+      </c>
+      <c r="AH8" s="6"/>
+      <c r="AI8" s="1">
+        <v>442</v>
+      </c>
+      <c r="AJ8" s="1">
+        <v>1963</v>
+      </c>
+      <c r="AK8" s="1">
+        <v>865</v>
+      </c>
+      <c r="AL8" s="1"/>
+      <c r="AM8" s="1"/>
+      <c r="AN8" s="2">
         <f t="shared" si="1"/>
-        <v>14270</v>
-      </c>
-      <c r="I8" s="1">
-        <v>606</v>
-      </c>
-      <c r="J8" s="1">
-        <v>1027</v>
-      </c>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-      <c r="Q8" s="1"/>
-      <c r="R8" s="1"/>
-      <c r="S8" s="1"/>
-      <c r="T8" s="1"/>
-      <c r="U8" s="6"/>
-      <c r="V8" s="1"/>
-      <c r="W8" s="1"/>
-      <c r="X8" s="1"/>
-      <c r="Y8" s="1"/>
-      <c r="Z8" s="1"/>
-      <c r="AA8" s="1"/>
-      <c r="AB8" s="6"/>
-      <c r="AC8" s="1"/>
-      <c r="AD8" s="1"/>
-      <c r="AE8" s="1"/>
-      <c r="AF8" s="1"/>
-      <c r="AG8" s="1"/>
-      <c r="AH8" s="1"/>
-      <c r="AI8" s="1"/>
-      <c r="AJ8" s="1"/>
-      <c r="AK8" s="1"/>
-      <c r="AL8" s="1"/>
-      <c r="AM8" s="2">
-        <f t="shared" si="2"/>
-        <v>1633</v>
-      </c>
-      <c r="AN8" s="4">
+        <v>35499</v>
+      </c>
+      <c r="AO8" s="4">
         <f t="shared" si="0"/>
-        <v>12637</v>
-      </c>
-    </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.35">
+        <v>22931</v>
+      </c>
+    </row>
+    <row r="9" spans="1:41" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="2">
         <v>60</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="21">
         <v>8</v>
       </c>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1">
-        <f t="shared" si="1"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="1">
+        <f>SUM(D9:H9)</f>
         <v>8</v>
       </c>
-      <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="1"/>
+      <c r="M9" s="23"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="25"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
-      <c r="T9" s="1"/>
-      <c r="U9" s="6"/>
-      <c r="V9" s="1"/>
+      <c r="T9" s="6"/>
+      <c r="U9" s="1"/>
+      <c r="V9" s="25"/>
       <c r="W9" s="1"/>
-      <c r="X9" s="1"/>
+      <c r="X9" s="6"/>
       <c r="Y9" s="1"/>
       <c r="Z9" s="1"/>
-      <c r="AA9" s="1"/>
-      <c r="AB9" s="6"/>
-      <c r="AC9" s="1"/>
+      <c r="AA9" s="6"/>
+      <c r="AB9" s="1"/>
+      <c r="AC9" s="25"/>
       <c r="AD9" s="1"/>
       <c r="AE9" s="1"/>
       <c r="AF9" s="1"/>
       <c r="AG9" s="1"/>
-      <c r="AH9" s="1"/>
+      <c r="AH9" s="6"/>
       <c r="AI9" s="1"/>
       <c r="AJ9" s="1"/>
       <c r="AK9" s="1"/>
       <c r="AL9" s="1"/>
-      <c r="AM9" s="2">
-        <f t="shared" si="2"/>
+      <c r="AM9" s="1"/>
+      <c r="AN9" s="2">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN9" s="4">
+      <c r="AO9" s="4">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.35">
       <c r="B10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="2">
+        <v>70</v>
+      </c>
+      <c r="D10" s="21"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2">
+        <v>26160</v>
+      </c>
+      <c r="I10" s="1">
+        <f>SUM(D10:H10)</f>
+        <v>26160</v>
+      </c>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="23"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="25"/>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="6"/>
+      <c r="U10" s="1"/>
+      <c r="V10" s="25"/>
+      <c r="W10" s="1"/>
+      <c r="X10" s="6"/>
+      <c r="Y10" s="1"/>
+      <c r="Z10" s="1"/>
+      <c r="AA10" s="6"/>
+      <c r="AB10" s="1"/>
+      <c r="AC10" s="25"/>
+      <c r="AD10" s="1"/>
+      <c r="AE10" s="1"/>
+      <c r="AF10" s="1"/>
+      <c r="AG10" s="1"/>
+      <c r="AH10" s="6"/>
+      <c r="AI10" s="1"/>
+      <c r="AJ10" s="1"/>
+      <c r="AK10" s="1"/>
+      <c r="AL10" s="1"/>
+      <c r="AM10" s="1"/>
+      <c r="AN10" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="AO10" s="4">
+        <f t="shared" si="0"/>
+        <v>26160</v>
+      </c>
+    </row>
+    <row r="11" spans="1:41" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="5">
-        <f>SUM(D3:D9)</f>
+      <c r="C11" s="1"/>
+      <c r="D11" s="20">
+        <f>SUM(D3:D10)</f>
         <v>43844</v>
       </c>
-      <c r="E10" s="5">
-        <f>SUM(E3:E9)</f>
+      <c r="E11" s="5">
+        <f>SUM(E3:E10)</f>
         <v>40000</v>
       </c>
-      <c r="F10" s="5">
-        <f>SUM(F3:F9)</f>
+      <c r="F11" s="5">
+        <f t="shared" ref="F11:H11" si="2">SUM(F3:F10)</f>
+        <v>40000</v>
+      </c>
+      <c r="G11" s="5">
+        <f t="shared" si="2"/>
+        <v>34400</v>
+      </c>
+      <c r="H11" s="5">
+        <f t="shared" si="2"/>
+        <v>46320</v>
+      </c>
+      <c r="I11" s="5">
+        <f>SUM(I3:I10)</f>
+        <v>204564</v>
+      </c>
+      <c r="J11" s="5">
+        <f t="shared" ref="J11:AO11" si="3">SUM(J3:J9)</f>
+        <v>3039</v>
+      </c>
+      <c r="K11" s="5">
+        <f t="shared" si="3"/>
+        <v>4112</v>
+      </c>
+      <c r="L11" s="5">
+        <f t="shared" si="3"/>
+        <v>3734</v>
+      </c>
+      <c r="M11" s="24">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G10" s="5">
-        <f>SUM(G3:G9)</f>
+      <c r="N11" s="5">
+        <f t="shared" si="3"/>
+        <v>1187</v>
+      </c>
+      <c r="O11" s="5">
+        <f t="shared" si="3"/>
+        <v>7167</v>
+      </c>
+      <c r="P11" s="5">
+        <f t="shared" si="3"/>
+        <v>6598</v>
+      </c>
+      <c r="Q11" s="5">
+        <f t="shared" si="3"/>
+        <v>4015</v>
+      </c>
+      <c r="R11" s="5">
+        <f t="shared" si="3"/>
+        <v>10854</v>
+      </c>
+      <c r="S11" s="5">
+        <f t="shared" si="3"/>
+        <v>3578</v>
+      </c>
+      <c r="T11" s="28">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H10" s="5">
-        <f>SUM(H3:H9)</f>
-        <v>83844</v>
-      </c>
-      <c r="I10" s="5">
-        <f t="shared" ref="I10:AN10" si="3">SUM(I3:I9)</f>
-        <v>3039</v>
-      </c>
-      <c r="J10" s="5">
-        <f t="shared" si="3"/>
-        <v>4112</v>
-      </c>
-      <c r="K10" s="5">
+      <c r="U11" s="5">
+        <f t="shared" si="3"/>
+        <v>6082</v>
+      </c>
+      <c r="V11" s="26">
+        <f t="shared" si="3"/>
+        <v>1687</v>
+      </c>
+      <c r="W11" s="5">
+        <f t="shared" si="3"/>
+        <v>1018</v>
+      </c>
+      <c r="X11" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L10" s="5">
+      <c r="Y11" s="5">
+        <f t="shared" si="3"/>
+        <v>16707</v>
+      </c>
+      <c r="Z11" s="5">
+        <f t="shared" si="3"/>
+        <v>8666</v>
+      </c>
+      <c r="AA11" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M10" s="5">
+      <c r="AB11" s="5">
+        <f t="shared" si="3"/>
+        <v>7967</v>
+      </c>
+      <c r="AC11" s="26">
+        <f t="shared" si="3"/>
+        <v>3121</v>
+      </c>
+      <c r="AD11" s="5">
+        <f t="shared" si="3"/>
+        <v>9033</v>
+      </c>
+      <c r="AE11" s="5">
+        <f t="shared" si="3"/>
+        <v>9758</v>
+      </c>
+      <c r="AF11" s="5">
+        <f t="shared" si="3"/>
+        <v>3989</v>
+      </c>
+      <c r="AG11" s="5">
+        <f t="shared" si="3"/>
+        <v>5071</v>
+      </c>
+      <c r="AH11" s="28">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N10" s="5">
+      <c r="AI11" s="5">
+        <f t="shared" si="3"/>
+        <v>1862</v>
+      </c>
+      <c r="AJ11" s="5">
+        <f t="shared" si="3"/>
+        <v>4398</v>
+      </c>
+      <c r="AK11" s="5">
+        <f t="shared" si="3"/>
+        <v>2769</v>
+      </c>
+      <c r="AL11" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O10" s="5">
+      <c r="AM11" s="5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P10" s="5">
-        <f t="shared" si="3"/>
+      <c r="AN11" s="5">
+        <f>SUM(AN3:AN10)</f>
+        <v>126412</v>
+      </c>
+      <c r="AO11" s="5">
+        <f>SUM(AO3:AO10)</f>
+        <v>78152</v>
+      </c>
+    </row>
+    <row r="12" spans="1:41" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="20">
+        <f>D11/40</f>
+        <v>1096.0999999999999</v>
+      </c>
+      <c r="E12" s="5">
+        <f>E11/40</f>
+        <v>1000</v>
+      </c>
+      <c r="F12" s="5">
+        <f>F11/40</f>
+        <v>1000</v>
+      </c>
+      <c r="G12" s="5">
+        <f>G11/40</f>
+        <v>860</v>
+      </c>
+      <c r="H12" s="5">
+        <f>H11/40</f>
+        <v>1158</v>
+      </c>
+      <c r="I12" s="15">
+        <f>I11/40</f>
+        <v>5114.1000000000004</v>
+      </c>
+      <c r="J12" s="5">
+        <f t="shared" ref="J12:AO12" si="4">J11/40</f>
+        <v>75.974999999999994</v>
+      </c>
+      <c r="K12" s="5">
+        <f t="shared" si="4"/>
+        <v>102.8</v>
+      </c>
+      <c r="L12" s="5">
+        <f t="shared" si="4"/>
+        <v>93.35</v>
+      </c>
+      <c r="M12" s="24">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="Q10" s="5">
-        <f t="shared" si="3"/>
+      <c r="N12" s="5">
+        <f t="shared" si="4"/>
+        <v>29.675000000000001</v>
+      </c>
+      <c r="O12" s="5">
+        <f t="shared" si="4"/>
+        <v>179.17500000000001</v>
+      </c>
+      <c r="P12" s="5">
+        <f t="shared" si="4"/>
+        <v>164.95</v>
+      </c>
+      <c r="Q12" s="5">
+        <f t="shared" si="4"/>
+        <v>100.375</v>
+      </c>
+      <c r="R12" s="5">
+        <f t="shared" si="4"/>
+        <v>271.35000000000002</v>
+      </c>
+      <c r="S12" s="5">
+        <f t="shared" si="4"/>
+        <v>89.45</v>
+      </c>
+      <c r="T12" s="28">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="R10" s="5">
-        <f t="shared" si="3"/>
+      <c r="U12" s="5">
+        <f t="shared" si="4"/>
+        <v>152.05000000000001</v>
+      </c>
+      <c r="V12" s="5">
+        <f t="shared" si="4"/>
+        <v>42.174999999999997</v>
+      </c>
+      <c r="W12" s="5">
+        <f t="shared" si="4"/>
+        <v>25.45</v>
+      </c>
+      <c r="X12" s="28">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S10" s="5">
-        <f t="shared" si="3"/>
+      <c r="Y12" s="5">
+        <f t="shared" si="4"/>
+        <v>417.67500000000001</v>
+      </c>
+      <c r="Z12" s="5">
+        <f t="shared" si="4"/>
+        <v>216.65</v>
+      </c>
+      <c r="AA12" s="28">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="T10" s="5">
-        <f t="shared" si="3"/>
+      <c r="AB12" s="5">
+        <f t="shared" si="4"/>
+        <v>199.17500000000001</v>
+      </c>
+      <c r="AC12" s="5">
+        <f t="shared" si="4"/>
+        <v>78.025000000000006</v>
+      </c>
+      <c r="AD12" s="5">
+        <f t="shared" si="4"/>
+        <v>225.82499999999999</v>
+      </c>
+      <c r="AE12" s="5">
+        <f t="shared" si="4"/>
+        <v>243.95</v>
+      </c>
+      <c r="AF12" s="5">
+        <f t="shared" si="4"/>
+        <v>99.724999999999994</v>
+      </c>
+      <c r="AG12" s="5">
+        <f t="shared" si="4"/>
+        <v>126.77500000000001</v>
+      </c>
+      <c r="AH12" s="28">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="U10" s="5">
-        <f t="shared" si="3"/>
+      <c r="AI12" s="5">
+        <f t="shared" si="4"/>
+        <v>46.55</v>
+      </c>
+      <c r="AJ12" s="5">
+        <f t="shared" si="4"/>
+        <v>109.95</v>
+      </c>
+      <c r="AK12" s="5">
+        <f t="shared" si="4"/>
+        <v>69.224999999999994</v>
+      </c>
+      <c r="AL12" s="5">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="V10" s="5">
-        <f t="shared" si="3"/>
+      <c r="AM12" s="5">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="W10" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="X10" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Y10" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Z10" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AA10" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AB10" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AC10" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AD10" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AE10" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AF10" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AG10" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AH10" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AI10" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AK10" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AL10" s="5">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AM10" s="5">
-        <f t="shared" si="3"/>
-        <v>7151</v>
-      </c>
-      <c r="AN10" s="5">
-        <f t="shared" si="3"/>
-        <v>76693</v>
-      </c>
-    </row>
-    <row r="11" spans="1:40" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="5">
-        <f>D10/40</f>
-        <v>1096.0999999999999</v>
-      </c>
-      <c r="E11" s="5">
-        <f>E10/40</f>
-        <v>1000</v>
-      </c>
-      <c r="F11" s="5">
-        <f>F10/40</f>
-        <v>0</v>
-      </c>
-      <c r="G11" s="5">
-        <f>G10/40</f>
-        <v>0</v>
-      </c>
-      <c r="H11" s="15">
-        <f>H10/40</f>
-        <v>2096.1</v>
-      </c>
-      <c r="I11" s="5">
-        <f t="shared" ref="I11:AN11" si="4">I10/40</f>
-        <v>75.974999999999994</v>
-      </c>
-      <c r="J11" s="5">
-        <f t="shared" si="4"/>
-        <v>102.8</v>
-      </c>
-      <c r="K11" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L11" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M11" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="N11" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="O11" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="P11" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Q11" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="R11" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S11" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="T11" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U11" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="V11" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="W11" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="X11" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Y11" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="Z11" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AA11" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AB11" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AC11" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AD11" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AE11" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AF11" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AG11" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AH11" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AI11" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AJ11" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AK11" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AL11" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="AM11" s="15">
-        <f t="shared" si="4"/>
-        <v>178.77500000000001</v>
-      </c>
-      <c r="AN11" s="16">
-        <f t="shared" si="4"/>
-        <v>1917.325</v>
-      </c>
-    </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.35">
-      <c r="A12" s="19" t="s">
+      <c r="AN12" s="15">
+        <f t="shared" si="4"/>
+        <v>3160.3</v>
+      </c>
+      <c r="AO12" s="16">
+        <f t="shared" si="4"/>
+        <v>1953.8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="A13" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="M12" s="17"/>
-    </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="N13" s="17"/>
+    </row>
+    <row r="14" spans="1:41" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B14" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-    </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.35">
-      <c r="A14" s="7"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-    </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+    </row>
+    <row r="15" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A15" s="7"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.35">
       <c r="A16" s="7"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="H16" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16">
+        <v>250</v>
+      </c>
+      <c r="J16">
+        <f>I16*40</f>
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" s="7"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="H17" t="s">
+        <v>25</v>
+      </c>
+      <c r="I17">
+        <v>254</v>
+      </c>
+      <c r="J17">
+        <f t="shared" ref="J17:J18" si="5">I17*40</f>
+        <v>10160</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="7"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="H18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I18">
+        <v>654</v>
+      </c>
+      <c r="J18">
+        <f>I18*40</f>
+        <v>26160</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="7"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="I19">
+        <f>SUM(I16:I18)</f>
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="7"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="7"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" s="7"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="7"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="7"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="7"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="7"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" s="7"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" s="7"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="7"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" s="7"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" s="7"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" s="7"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1801,7 +2234,7 @@
       <c r="D55" s="1"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" s="1"/>
+      <c r="A56" s="7"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
@@ -1921,20 +2354,26 @@
       <c r="D75" s="1"/>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A76" s="1" t="s">
+      <c r="A76" s="1"/>
+      <c r="B76" s="1"/>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A77" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B76" s="1"/>
-      <c r="C76" s="4">
-        <f>SUM(C14:C75)</f>
+      <c r="B77" s="1"/>
+      <c r="C77" s="4">
+        <f>SUM(C15:C76)</f>
         <v>0</v>
       </c>
-      <c r="D76" s="1"/>
+      <c r="D77" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B1:AN1"/>
-    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="B1:AO1"/>
+    <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
